--- a/Side Bar Files/GWD Data/Panel Board.xlsx
+++ b/Side Bar Files/GWD Data/Panel Board.xlsx
@@ -312,8 +312,12 @@
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -737,7 +741,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5E796F0-5B76-4AA5-AA81-BA5A3511B9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24403741-EC14-46BA-B59E-B6E073A8B9A7}">
   <dimension ref="A1:G57"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/Panel Board.xlsx
+++ b/Side Bar Files/GWD Data/Panel Board.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="48">
   <si>
     <t>Panel Board</t>
   </si>
@@ -66,6 +66,9 @@
   </si>
   <si>
     <t>3 Pole Capacitor duty contactors for switching capacitor banks 4 - 7 kVAR with AC Coil</t>
+  </si>
+  <si>
+    <t>0</t>
   </si>
   <si>
     <t>Nut &amp; Bolt</t>
@@ -282,25 +285,11 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment/>
       <protection/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -360,11 +349,11 @@
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="15" builtinId="5"/>
-    <cellStyle name="Currency" xfId="16" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
-    <cellStyle name="Comma" xfId="18" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="3" builtinId="7"/>
+    <cellStyle name="Comma" xfId="4" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="5" builtinId="6"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -741,7 +730,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24403741-EC14-46BA-B59E-B6E073A8B9A7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC55CA0C-2E06-41E6-AC64-FCDB9D06BAA6}">
   <dimension ref="A1:G57"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
@@ -915,22 +904,22 @@
     </row>
     <row r="9" spans="1:7" ht="12.75">
       <c r="A9" s="6" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" s="8">
         <v>1</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E9" s="8">
         <v>100</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G9" s="10">
         <f>C9*E9</f>
@@ -939,10 +928,10 @@
     </row>
     <row r="10" spans="1:7" ht="12.75">
       <c r="A10" s="6" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" s="8">
         <v>1</v>
@@ -964,7 +953,7 @@
     <row r="11" spans="1:7" ht="12.75">
       <c r="A11" s="6"/>
       <c r="B11" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
@@ -978,7 +967,7 @@
     <row r="12" spans="1:7" ht="12.75">
       <c r="A12" s="6"/>
       <c r="B12" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
@@ -992,7 +981,7 @@
     <row r="13" spans="1:7" ht="12.75">
       <c r="A13" s="6"/>
       <c r="B13" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
@@ -1006,7 +995,7 @@
     <row r="14" spans="1:7" ht="12.75">
       <c r="A14" s="6"/>
       <c r="B14" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
@@ -1020,7 +1009,7 @@
     <row r="15" spans="1:7" ht="12.75">
       <c r="A15" s="6"/>
       <c r="B15" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
@@ -1033,22 +1022,22 @@
     </row>
     <row r="16" spans="1:7" ht="12.75">
       <c r="A16" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" s="8">
         <v>1</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E16" s="14">
         <v>383</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G16" s="10">
         <f>C16*E16</f>
@@ -1057,10 +1046,10 @@
     </row>
     <row r="17" spans="1:7" ht="12.75">
       <c r="A17" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C17" s="8">
         <v>1</v>
@@ -1081,22 +1070,22 @@
     </row>
     <row r="18" spans="1:7" ht="12.75">
       <c r="A18" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C18" s="8">
         <v>1.15</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E18" s="14">
         <v>612</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G18" s="10">
         <f>C18*E18</f>
@@ -1105,22 +1094,22 @@
     </row>
     <row r="19" spans="1:7" ht="12.75">
       <c r="A19" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C19" s="8">
         <v>10</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E19" s="14">
         <v>28</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G19" s="10">
         <f>C19*E19</f>
@@ -1129,22 +1118,22 @@
     </row>
     <row r="20" spans="1:7" ht="12.75">
       <c r="A20" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C20" s="8">
         <v>1</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E20" s="8">
         <v>784</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G20" s="10">
         <f>C20*E20</f>
@@ -1153,22 +1142,22 @@
     </row>
     <row r="21" spans="1:7" ht="12.75">
       <c r="A21" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C21" s="8">
         <v>1</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E21" s="8">
         <v>645</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G21" s="10">
         <f>C21*E21</f>
@@ -1178,7 +1167,7 @@
     <row r="22" spans="1:7" ht="12.75">
       <c r="A22" s="15"/>
       <c r="B22" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
@@ -1192,7 +1181,7 @@
     <row r="23" spans="1:7" ht="12.75">
       <c r="A23" s="15"/>
       <c r="B23" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
@@ -1206,7 +1195,7 @@
     <row r="24" spans="1:7" ht="12.75">
       <c r="A24" s="15"/>
       <c r="B24" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
@@ -1219,22 +1208,22 @@
     </row>
     <row r="25" spans="1:7" ht="12.75">
       <c r="A25" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C25" s="8">
         <v>1</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E25" s="8">
         <v>806</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G25" s="10">
         <f>C25*E25</f>
@@ -1244,7 +1233,7 @@
     <row r="26" spans="1:7" ht="12.75">
       <c r="A26" s="15"/>
       <c r="B26" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
@@ -1258,7 +1247,7 @@
     <row r="27" spans="1:7" ht="12.75">
       <c r="A27" s="15"/>
       <c r="B27" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
@@ -1272,7 +1261,7 @@
     <row r="28" spans="1:7" ht="12.75">
       <c r="A28" s="15"/>
       <c r="B28" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
@@ -1297,10 +1286,10 @@
     </row>
     <row r="30" spans="1:7" ht="12.75">
       <c r="A30" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
@@ -1310,7 +1299,7 @@
     </row>
     <row r="31" spans="1:7" ht="12.75">
       <c r="A31" s="6" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>4</v>
@@ -1454,22 +1443,22 @@
     </row>
     <row r="37" spans="1:7" ht="12.75">
       <c r="A37" s="6" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C37" s="8">
         <v>1</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E37" s="8">
         <v>100</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G37" s="10">
         <f>C37*E37</f>
@@ -1478,10 +1467,10 @@
     </row>
     <row r="38" spans="1:7" ht="12.75">
       <c r="A38" s="6" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C38" s="8">
         <v>1</v>
@@ -1503,7 +1492,7 @@
     <row r="39" spans="1:7" ht="12.75">
       <c r="A39" s="6"/>
       <c r="B39" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
@@ -1517,7 +1506,7 @@
     <row r="40" spans="1:7" ht="12.75">
       <c r="A40" s="6"/>
       <c r="B40" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
@@ -1531,7 +1520,7 @@
     <row r="41" spans="1:7" ht="12.75">
       <c r="A41" s="6"/>
       <c r="B41" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
@@ -1545,7 +1534,7 @@
     <row r="42" spans="1:7" ht="12.75">
       <c r="A42" s="6"/>
       <c r="B42" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C42" s="8"/>
       <c r="D42" s="8"/>
@@ -1559,7 +1548,7 @@
     <row r="43" spans="1:7" ht="12.75">
       <c r="A43" s="6"/>
       <c r="B43" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
@@ -1572,22 +1561,22 @@
     </row>
     <row r="44" spans="1:7" ht="12.75">
       <c r="A44" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C44" s="8">
         <v>1</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E44" s="14">
         <v>383</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G44" s="10">
         <f>C44*E44</f>
@@ -1596,10 +1585,10 @@
     </row>
     <row r="45" spans="1:7" ht="12.75">
       <c r="A45" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C45" s="8">
         <v>1</v>
@@ -1620,22 +1609,22 @@
     </row>
     <row r="46" spans="1:7" ht="12.75">
       <c r="A46" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C46" s="8">
         <v>1.15</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E46" s="14">
         <v>612</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G46" s="10">
         <f>C46*E46</f>
@@ -1644,22 +1633,22 @@
     </row>
     <row r="47" spans="1:7" ht="12.75">
       <c r="A47" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C47" s="8">
         <v>15</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E47" s="14">
         <v>28</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G47" s="10">
         <f>C47*E47</f>
@@ -1668,22 +1657,22 @@
     </row>
     <row r="48" spans="1:7" ht="12.75">
       <c r="A48" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C48" s="8">
         <v>2</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E48" s="8">
         <v>784</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G48" s="10">
         <f>C48*E48</f>
@@ -1692,22 +1681,22 @@
     </row>
     <row r="49" spans="1:7" ht="12.75">
       <c r="A49" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C49" s="8">
         <v>2</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E49" s="8">
         <v>645</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G49" s="10">
         <f>C49*E49</f>
@@ -1717,7 +1706,7 @@
     <row r="50" spans="1:7" ht="12.75">
       <c r="A50" s="15"/>
       <c r="B50" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C50" s="8"/>
       <c r="D50" s="8"/>
@@ -1731,7 +1720,7 @@
     <row r="51" spans="1:7" ht="12.75">
       <c r="A51" s="15"/>
       <c r="B51" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C51" s="8"/>
       <c r="D51" s="8"/>
@@ -1745,7 +1734,7 @@
     <row r="52" spans="1:7" ht="12.75">
       <c r="A52" s="15"/>
       <c r="B52" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C52" s="8"/>
       <c r="D52" s="8"/>
@@ -1758,22 +1747,22 @@
     </row>
     <row r="53" spans="1:7" ht="12.75">
       <c r="A53" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C53" s="8">
         <v>2</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E53" s="8">
         <v>806</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G53" s="10">
         <f>C53*E53</f>
@@ -1783,7 +1772,7 @@
     <row r="54" spans="1:7" ht="12.75">
       <c r="A54" s="15"/>
       <c r="B54" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C54" s="8"/>
       <c r="D54" s="8"/>
@@ -1797,7 +1786,7 @@
     <row r="55" spans="1:7" ht="12.75">
       <c r="A55" s="15"/>
       <c r="B55" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C55" s="8"/>
       <c r="D55" s="8"/>
@@ -1811,7 +1800,7 @@
     <row r="56" spans="1:7" ht="12.75">
       <c r="A56" s="15"/>
       <c r="B56" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C56" s="8"/>
       <c r="D56" s="8"/>

--- a/Side Bar Files/GWD Data/Panel Board.xlsx
+++ b/Side Bar Files/GWD Data/Panel Board.xlsx
@@ -730,7 +730,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC55CA0C-2E06-41E6-AC64-FCDB9D06BAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{229902B9-76B8-47C1-9AF8-35A5F352BAA6}">
   <dimension ref="A1:G57"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/Panel Board.xlsx
+++ b/Side Bar Files/GWD Data/Panel Board.xlsx
@@ -730,7 +730,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{229902B9-76B8-47C1-9AF8-35A5F352BAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71A5B81C-5037-4482-B84E-AE901EC2BAA6}">
   <dimension ref="A1:G57"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
